--- a/financial_advisor_forms/001_financial_application_form--financial_advisor_forms.xlsx
+++ b/financial_advisor_forms/001_financial_application_form--financial_advisor_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,109 +515,109 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>financial_application_form_1</t>
+          <t>employment_status</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>financial_applicant_info</t>
+          <t>What is your employment status?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>financial_application_form_2</t>
+          <t>education_level</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>financial_institution</t>
+          <t>What is your education level?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>financial_application_form_3</t>
+          <t>income_level</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>financial_institution</t>
+          <t>What is your financial income level?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>financial_application_form_4</t>
+          <t>income_frequency</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>credit_score</t>
+          <t>How frequently do you earn your income?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>financial_application_form_5</t>
+          <t>property_type</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>employment_status</t>
+          <t>What type of property do you own?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,18 +635,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>financial_application_form_6</t>
+          <t>property_age</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>employment_length</t>
+          <t>How old is the property?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>financial_application_form_7</t>
+          <t>property_value</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>financial_history</t>
+          <t>What is the value of the property?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,109 +676,109 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>financial_application_form_8</t>
+          <t>property_city</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>financial_education_level</t>
+          <t>Where is the property located?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>financial_application_form_9</t>
+          <t>property_state</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>financial_employed_status</t>
+          <t>State?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>financial_application_form_10</t>
+          <t>property_country</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>financial_income_level</t>
+          <t>Country?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>financial_application_form_11</t>
+          <t>property_zip</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>financial_income_frequency</t>
+          <t>Zip?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>financial_application_form_12</t>
+          <t>property_notes</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>financial_property_type</t>
+          <t>Additional notes about the property?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,297 +791,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>financial_application_form_13</t>
+          <t>additional_property_notes</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>financial_property_age</t>
+          <t>Do you have any additional information about the property?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>financial_application_form_14</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>financial_property_value</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>financial_application_form_15</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>financial_property_address</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>financial_application_form_16</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>financial_property_city</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>financial_application_form_17</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>financial_property_state</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>financial_application_form_18</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>financial_property_country</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>financial_application_form_19</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>financial_property_zip</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>financial_application_form_20</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>financial_property_type</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>financial_application_form_21</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>financial_property_age</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>financial_application_form_22</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>financial_property_mortgage_type</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>financial_application_form_23</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>financial_application_form_23</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>financial_application_form_24</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>financial_property_notes</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>financial_application_form_25</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>financial_property_additional_notes</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +822,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="39" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,491 +850,355 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>financial_application_form_5_choices</t>
+          <t>employment_status_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'employed'}</t>
+          <t>employed</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'employed'}</t>
+          <t>Employed</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>financial_application_form_5_choices</t>
+          <t>employment_status_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'unemployed'}</t>
+          <t>unemployed</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'unemployed'}</t>
+          <t>Unemployed</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>financial_application_form_5_choices</t>
+          <t>employment_status_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'self_employed'}</t>
+          <t>self-employed</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'self_employed'}</t>
+          <t>Self-employed</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>financial_application_form_8_choices</t>
+          <t>employment_status_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'high_school'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'high_school'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>financial_application_form_8_choices</t>
+          <t>education_level_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'college'}</t>
+          <t>high_school</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'college'}</t>
+          <t>High school</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>financial_application_form_8_choices</t>
+          <t>education_level_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'graduate'}</t>
+          <t>college</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'graduate'}</t>
+          <t>College</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>financial_application_form_8_choices</t>
+          <t>education_level_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'some_college'}</t>
+          <t>graduate</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'some_college'}</t>
+          <t>Graduate</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>financial_application_form_8_choices</t>
+          <t>education_level_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>some_college</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'other'}</t>
+          <t>Some college</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>financial_application_form_9_choices</t>
+          <t>education_level_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'employed'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'employed'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>financial_application_form_9_choices</t>
+          <t>income_level_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'self_employed'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'self_employed'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>financial_application_form_9_choices</t>
+          <t>income_level_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'retired'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'retired'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>financial_application_form_9_choices</t>
+          <t>income_level_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'unemployed'}</t>
+          <t>moderate</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'unemployed'}</t>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>financial_application_form_9_choices</t>
+          <t>income_level_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>very_high</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'other'}</t>
+          <t>Very high</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>financial_application_form_10_choices</t>
+          <t>income_level_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'low'}</t>
+          <t>very_low</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'low'}</t>
+          <t>Very low</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>financial_application_form_10_choices</t>
+          <t>income_level_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'high'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'high'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>financial_application_form_10_choices</t>
+          <t>income_frequency_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'moderate'}</t>
+          <t>yearly</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'moderate'}</t>
+          <t>Yearly</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>financial_application_form_10_choices</t>
+          <t>income_frequency_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'very_high'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'very_high'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>financial_application_form_10_choices</t>
+          <t>income_frequency_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'very_moderate'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'very_moderate'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>financial_application_form_10_choices</t>
+          <t>income_frequency_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'other'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>financial_application_form_11_choices</t>
+          <t>property_type_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'yearly'}</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'yearly'}</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>financial_application_form_11_choices</t>
+          <t>property_type_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'monthly'}</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
-        <is>
-          <t>{'value': 'monthly'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>financial_application_form_11_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>{'value':_'weekly'}</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>{'value': 'weekly'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>financial_application_form_11_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>{'value':_'daily'}</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>{'value': 'daily'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>financial_application_form_12_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>financial_application_form_12_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>financial_application_form_20_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>financial_application_form_20_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>financial_application_form_22_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>financial_application_form_22_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
         <is>
           <t>No</t>
         </is>
